--- a/data/trans_orig/IP3107-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP3107-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9809</t>
+          <t>10047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>10065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>598</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>720</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14012</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8941</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59542</t>
+          <t>59667</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>71480</t>
+          <t>71632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>62088</t>
+          <t>61155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72550</t>
+          <t>72600</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>124424</t>
+          <t>125436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141363</t>
+          <t>141425</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,64%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8359</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19189</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16032</t>
+          <t>15798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>30200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>709</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7028</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9236</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7146</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>11890</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4053</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41985</t>
+          <t>42193</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54947</t>
+          <t>54875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49246</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>60315</t>
+          <t>59906</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94168</t>
+          <t>94225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112742</t>
+          <t>111546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11217</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>22974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17087</t>
+          <t>17519</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31595</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7123</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10090</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13954</t>
+          <t>14224</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>817</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1597</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8450</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38874</t>
+          <t>37779</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49090</t>
+          <t>48547</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50806</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65206</t>
+          <t>65379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94102</t>
+          <t>94266</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111489</t>
+          <t>111169</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,61%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19155</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34110</t>
+          <t>34298</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28016</t>
+          <t>28480</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44728</t>
+          <t>44532</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51852</t>
+          <t>51671</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74517</t>
+          <t>74496</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,4%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>8929</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20428</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>19193</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8847</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20276</t>
+          <t>20762</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>19566</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>35483</t>
+          <t>35696</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>11179</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11763</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>7510</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18998</t>
+          <t>19416</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112723</t>
+          <t>112238</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131490</t>
+          <t>131783</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>100767</t>
+          <t>100074</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>119478</t>
+          <t>120283</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>218829</t>
+          <t>217641</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>245768</t>
+          <t>246288</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10336</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22459</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29348</t>
+          <t>29628</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>29058</t>
+          <t>28508</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46668</t>
+          <t>46093</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>9380</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>15042</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15870</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24104</t>
+          <t>23665</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>454</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>56692</t>
+          <t>56973</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>70909</t>
+          <t>71060</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>64707</t>
+          <t>64034</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>79847</t>
+          <t>80831</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>125729</t>
+          <t>126863</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>146804</t>
+          <t>147805</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,45%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8830</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>19233</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>15612</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>17388</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>32338</t>
+          <t>32040</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -4290,47 +4290,47 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5454</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
           <t>647</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>5417</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>14627</t>
+          <t>14544</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>767</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5979</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,47 +4496,47 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>8,69%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5451</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>5239</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>40316</t>
+          <t>40416</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>53564</t>
+          <t>53365</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>35520</t>
+          <t>34840</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>46369</t>
+          <t>46351</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>79926</t>
+          <t>80823</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>97408</t>
+          <t>96472</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>72840</t>
+          <t>72568</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>100716</t>
+          <t>100244</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>84336</t>
+          <t>86110</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>113499</t>
+          <t>115103</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>167115</t>
+          <t>164400</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>207076</t>
+          <t>205530</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>24479</t>
+          <t>23153</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>14547</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>28694</t>
+          <t>28587</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>28764</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>46993</t>
+          <t>47142</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>27446</t>
+          <t>27732</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>47094</t>
+          <t>47088</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>31128</t>
+          <t>30839</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>50176</t>
+          <t>50201</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>63523</t>
+          <t>62906</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>89090</t>
+          <t>88873</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>12326</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>25940</t>
+          <t>26627</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>30891</t>
+          <t>30533</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>30549</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>50642</t>
+          <t>50888</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>375604</t>
+          <t>376309</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>408790</t>
+          <t>409839</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>387415</t>
+          <t>386232</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>423110</t>
+          <t>422788</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,08%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>774686</t>
+          <t>774515</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>822730</t>
+          <t>823760</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,46%</t>
         </is>
       </c>
     </row>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23597</t>
+          <t>22758</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,39 +5868,39 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3287</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3844</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>10703</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6425</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17503</t>
+          <t>16481</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13026</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48454</t>
+          <t>48392</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61341</t>
+          <t>60886</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50144</t>
+          <t>50313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61747</t>
+          <t>61852</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101430</t>
+          <t>103431</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>120235</t>
+          <t>119832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,34%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9372</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>620</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6590,7 +6590,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16803</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9713</t>
+          <t>8873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58966</t>
+          <t>58647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69563</t>
+          <t>69186</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63635</t>
+          <t>64299</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75223</t>
+          <t>75359</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124217</t>
+          <t>125644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141712</t>
+          <t>140956</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,31%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>670</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20134</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11848</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,12 +7302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11921</t>
+          <t>12378</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11340</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6179</t>
+          <t>6032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>16246</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50715</t>
+          <t>50477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>61441</t>
+          <t>61583</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37709</t>
+          <t>38676</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51698</t>
+          <t>52461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92371</t>
+          <t>91082</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110440</t>
+          <t>110154</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9768</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22051</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11485</t>
+          <t>12184</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24094</t>
+          <t>24131</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42286</t>
+          <t>41626</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>22832</t>
+          <t>22471</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4434</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9094</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21246</t>
+          <t>21833</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16045</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30589</t>
+          <t>31440</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>14695</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>16083</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11951</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25653</t>
+          <t>27493</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>117923</t>
+          <t>118387</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>136112</t>
+          <t>136424</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>126983</t>
+          <t>128066</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>147802</t>
+          <t>148973</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>251859</t>
+          <t>251843</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>279066</t>
+          <t>280013</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15762</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>12977</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>27158</t>
+          <t>26342</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8636,7 +8636,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15719</t>
+          <t>15668</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>26725</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22557</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>41586</t>
+          <t>39852</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12545</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>15266</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>24376</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>86674</t>
+          <t>85843</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>103070</t>
+          <t>102779</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>68672</t>
+          <t>68890</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>86341</t>
+          <t>86039</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>160562</t>
+          <t>161128</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>184196</t>
+          <t>184508</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>9077</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>5041</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9283,7 +9283,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7381</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>7669</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>3284</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>28223</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>37448</t>
+          <t>37775</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>42385</t>
+          <t>42234</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>53637</t>
+          <t>53804</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>74072</t>
+          <t>74655</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>89446</t>
+          <t>89451</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>34625</t>
+          <t>35702</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>54454</t>
+          <t>55632</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>39350</t>
+          <t>38888</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>60269</t>
+          <t>60892</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>78573</t>
+          <t>78466</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>108623</t>
+          <t>108627</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,7 +9917,7 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>31814</t>
+          <t>32078</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>11367</t>
+          <t>11214</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>25695</t>
+          <t>25160</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>31748</t>
+          <t>30930</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>52908</t>
+          <t>52556</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>29457</t>
+          <t>29098</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>48880</t>
+          <t>49473</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>46804</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>71316</t>
+          <t>70988</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>83171</t>
+          <t>82061</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>114626</t>
+          <t>114146</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>19283</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>35390</t>
+          <t>36360</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>27842</t>
+          <t>28599</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>47637</t>
+          <t>48078</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>52776</t>
+          <t>51433</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>76911</t>
+          <t>76959</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>416189</t>
+          <t>416367</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>448172</t>
+          <t>449202</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>420998</t>
+          <t>418500</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>455177</t>
+          <t>454693</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>843770</t>
+          <t>842982</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>894058</t>
+          <t>893935</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>15201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>6625</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2422</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>9709</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>7128</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18713</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54594</t>
+          <t>55056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65508</t>
+          <t>64853</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68263</t>
+          <t>67946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79385</t>
+          <t>79246</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>127124</t>
+          <t>126503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142186</t>
+          <t>142210</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,84%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>11424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>14997</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,7%</t>
         </is>
       </c>
     </row>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7091</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11443</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15826</t>
+          <t>15419</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>7199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17743</t>
+          <t>18186</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71008</t>
+          <t>71184</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82474</t>
+          <t>82253</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77498</t>
+          <t>77977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>90373</t>
+          <t>90953</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152977</t>
+          <t>154171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170326</t>
+          <t>170895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8395</t>
+          <t>8145</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2933</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12300,7 +12300,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8487</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,49 +12466,49 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>16,24%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>5839</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2952</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10862</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
           <t>15,48%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5839</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2644</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9933</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>8,32%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>14,16%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>16</t>
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16548</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,07%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38216</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48004</t>
+          <t>47810</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52402</t>
+          <t>52514</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62747</t>
+          <t>62518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94141</t>
+          <t>94698</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>107828</t>
+          <t>108701</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22311</t>
+          <t>21572</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18781</t>
+          <t>19424</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35045</t>
+          <t>34747</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>479</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12962,7 +12962,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1663</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18801</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>8895</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>20448</t>
+          <t>21224</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>36311</t>
+          <t>35222</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20922</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14326</t>
+          <t>14218</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>152863</t>
+          <t>152944</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>171379</t>
+          <t>170210</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>145779</t>
+          <t>145581</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163616</t>
+          <t>163038</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>304161</t>
+          <t>305094</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>329198</t>
+          <t>330139</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13935</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3516</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>13110</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23943</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>9533</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13769</t>
+          <t>14190</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8466</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18738</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11820</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12424</t>
+          <t>12080</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>25866</t>
+          <t>25775</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>93204</t>
+          <t>92943</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>108260</t>
+          <t>107640</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>102173</t>
+          <t>101488</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>116656</t>
+          <t>116625</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>199803</t>
+          <t>200743</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>221242</t>
+          <t>221431</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,18%</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>573</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -14389,7 +14389,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11435</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>16258</t>
+          <t>14801</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>41399</t>
+          <t>40730</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>50252</t>
+          <t>50095</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>42864</t>
+          <t>42345</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>53405</t>
+          <t>54053</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>86428</t>
+          <t>87464</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>100970</t>
+          <t>102129</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>28298</t>
+          <t>28714</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>47417</t>
+          <t>47538</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>26606</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>47245</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>60088</t>
+          <t>59784</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>86750</t>
+          <t>87374</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>14052</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>17792</t>
+          <t>18536</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>14078</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>28436</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>30169</t>
+          <t>29902</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>26456</t>
+          <t>26887</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>45254</t>
+          <t>46789</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>45678</t>
+          <t>45771</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>71277</t>
+          <t>69084</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>36370</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>57182</t>
+          <t>56627</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>27542</t>
+          <t>27574</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>46547</t>
+          <t>46219</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>69472</t>
+          <t>70060</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>98773</t>
+          <t>97288</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>474674</t>
+          <t>475295</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>506267</t>
+          <t>505070</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>514874</t>
+          <t>513133</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>547153</t>
+          <t>546050</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>999873</t>
+          <t>1000544</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1044287</t>
+          <t>1046315</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,39%</t>
         </is>
       </c>
     </row>
